--- a/turucar_wash/차량소속별_밴드매칭.xlsx
+++ b/turucar_wash/차량소속별_밴드매칭.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\winn\Desktop\세차\세차 대상 리스트\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\winn\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F9C3FA4-464B-4A31-95BF-C7C6FBA7C5B5}" xr6:coauthVersionLast="41" xr6:coauthVersionMax="41" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{CE96C6F0-42D5-4A21-8DA8-23C13BE94697}" xr6:coauthVersionLast="41" xr6:coauthVersionMax="41" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{62353199-A8FC-4D29-9BCD-0E29239A9303}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="63">
   <si>
     <t>해피투어</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -225,6 +225,55 @@
   </si>
   <si>
     <t>https://www.band.us/band/86323890/post</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>타고렌터카</t>
+  </si>
+  <si>
+    <t>내차처럼렌터카</t>
+  </si>
+  <si>
+    <t>서경투어엔카</t>
+  </si>
+  <si>
+    <t>코리아렌터카</t>
+  </si>
+  <si>
+    <t>픽스렌트카</t>
+  </si>
+  <si>
+    <t>픽스렌트카(프로모션)</t>
+  </si>
+  <si>
+    <t>곰두리렌터카</t>
+  </si>
+  <si>
+    <t>나예</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.band.us/band/103096204/post</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.band.us/band/89471014/post</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.band.us/band/101002867/post</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.band.us/band/86323890/post</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.band.us/band/98314859/post</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.band.us/band/100842077/post</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -232,7 +281,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -258,26 +307,72 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="10"/>
+      <sz val="9"/>
+      <color theme="1"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color theme="1"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="9"/>
+      <color theme="10"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
       <color theme="1"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="0" tint="-0.34998626667073579"/>
+      </left>
+      <right style="thin">
+        <color theme="0" tint="-0.34998626667073579"/>
+      </right>
+      <top style="thin">
+        <color theme="0" tint="-0.34998626667073579"/>
+      </top>
+      <bottom style="thin">
+        <color theme="0" tint="-0.34998626667073579"/>
+      </bottom>
       <diagonal/>
     </border>
   </borders>
@@ -289,14 +384,26 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -614,7 +721,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A45666EB-1DC4-467A-A95D-B61AE921C119}">
-  <dimension ref="A1:C44"/>
+  <dimension ref="A1:C52"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="21.296875" bestFit="1" customWidth="1"/>
@@ -623,431 +730,521 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A1" t="s">
+      <c r="A1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A2" t="s">
+      <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="B2" s="1"/>
+      <c r="C2" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A3" t="s">
+      <c r="A3" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="B3" s="1"/>
+      <c r="C3" s="2" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A4" t="s">
+      <c r="A4" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="B4" s="1"/>
+      <c r="C4" s="2" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A5" t="s">
+      <c r="A5" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C5" s="1" t="s">
+      <c r="B5" s="1"/>
+      <c r="C5" s="2" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A6" t="s">
+      <c r="A6" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C6" s="1" t="s">
+      <c r="B6" s="1"/>
+      <c r="C6" s="2" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A7" t="s">
+      <c r="A7" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="C7" s="1" t="s">
+      <c r="B7" s="1"/>
+      <c r="C7" s="2" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A8" t="s">
+      <c r="A8" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="C8" s="1" t="s">
+      <c r="B8" s="1"/>
+      <c r="C8" s="2" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A9" t="s">
+      <c r="A9" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="C9" s="1" t="s">
+      <c r="B9" s="1"/>
+      <c r="C9" s="2" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A10" t="s">
+      <c r="A10" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="C10" s="1" t="s">
+      <c r="B10" s="1"/>
+      <c r="C10" s="2" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A11" t="s">
+      <c r="A11" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="C11" s="1" t="s">
+      <c r="B11" s="1"/>
+      <c r="C11" s="2" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A12" s="2" t="s">
+      <c r="A12" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="B12" s="2"/>
-      <c r="C12" s="1" t="s">
+      <c r="B12" s="3"/>
+      <c r="C12" s="2" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A13" t="s">
+      <c r="A13" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="C13" s="1" t="s">
+      <c r="B13" s="1"/>
+      <c r="C13" s="2" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A14" t="s">
+      <c r="A14" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="B14" t="s">
+      <c r="B14" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="C14" s="1" t="s">
+      <c r="C14" s="2" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A15" t="s">
+      <c r="A15" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="B15" t="s">
+      <c r="B15" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="C15" s="1" t="s">
+      <c r="C15" s="2" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A16" t="s">
+      <c r="A16" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="B16" t="s">
+      <c r="B16" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="C16" s="1" t="s">
+      <c r="C16" s="2" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A17" t="s">
+      <c r="A17" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="B17" t="s">
+      <c r="B17" s="1" t="s">
         <v>33</v>
       </c>
+      <c r="C17" s="1"/>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A18" t="s">
+      <c r="A18" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="B18" t="s">
+      <c r="B18" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="C18" s="1" t="s">
+      <c r="C18" s="2" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A19" t="s">
+      <c r="A19" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="B19" t="s">
+      <c r="B19" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="C19" s="1" t="s">
+      <c r="C19" s="2" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A20" t="s">
+      <c r="A20" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="B20" t="s">
+      <c r="B20" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="C20" s="1" t="s">
+      <c r="C20" s="2" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A21" t="s">
+      <c r="A21" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="B21" t="s">
+      <c r="B21" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="C21" s="1" t="s">
+      <c r="C21" s="2" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A22" t="s">
+      <c r="A22" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="B22" t="s">
+      <c r="B22" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="C22" s="1" t="s">
+      <c r="C22" s="2" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A23" t="s">
+      <c r="A23" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="B23" t="s">
+      <c r="B23" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="C23" s="1" t="s">
+      <c r="C23" s="2" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A24" t="s">
+      <c r="A24" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="B24" t="s">
+      <c r="B24" s="1" t="s">
         <v>33</v>
       </c>
+      <c r="C24" s="1"/>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A25" t="s">
+      <c r="A25" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="B25" t="s">
+      <c r="B25" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="C25" s="1" t="s">
+      <c r="C25" s="2" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A26" t="s">
+      <c r="A26" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="B26" t="s">
+      <c r="B26" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="C26" s="1" t="s">
+      <c r="C26" s="2" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A27" t="s">
+      <c r="A27" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="B27" t="s">
+      <c r="B27" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="C27" s="1" t="s">
+      <c r="C27" s="2" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A28" t="s">
+      <c r="A28" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="B28" t="s">
+      <c r="B28" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="C28" s="1" t="s">
+      <c r="C28" s="2" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A29" t="s">
+      <c r="A29" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="B29" t="s">
+      <c r="B29" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="C29" s="1" t="s">
+      <c r="C29" s="2" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A30" t="s">
+      <c r="A30" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="B30" t="s">
+      <c r="B30" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="C30" s="1" t="s">
+      <c r="C30" s="2" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A31" t="s">
+      <c r="A31" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="B31" t="s">
+      <c r="B31" s="1" t="s">
         <v>33</v>
       </c>
+      <c r="C31" s="1"/>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A32" t="s">
+      <c r="A32" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="B32" t="s">
+      <c r="B32" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="C32" s="1" t="s">
+      <c r="C32" s="2" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A33" t="s">
+      <c r="A33" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="B33" t="s">
+      <c r="B33" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="C33" s="1" t="s">
+      <c r="C33" s="2" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A34" t="s">
+      <c r="A34" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="B34" t="s">
+      <c r="B34" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="C34" s="1" t="s">
+      <c r="C34" s="2" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A35" t="s">
+      <c r="A35" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="B35" t="s">
+      <c r="B35" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="C35" s="1" t="s">
+      <c r="C35" s="2" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A36" t="s">
+      <c r="A36" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="B36" t="s">
+      <c r="B36" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="C36" s="1" t="s">
+      <c r="C36" s="2" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A37" t="s">
+      <c r="A37" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="B37" t="s">
+      <c r="B37" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="C37" s="1" t="s">
+      <c r="C37" s="2" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A38" t="s">
+      <c r="A38" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="B38" t="s">
+      <c r="B38" s="1" t="s">
         <v>33</v>
       </c>
+      <c r="C38" s="1"/>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A39" t="s">
+      <c r="A39" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="B39" t="s">
+      <c r="B39" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="C39" s="1" t="s">
+      <c r="C39" s="2" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A40" t="s">
+      <c r="A40" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="B40" t="s">
+      <c r="B40" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="C40" s="1" t="s">
+      <c r="C40" s="2" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A41" t="s">
+      <c r="A41" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="B41" t="s">
+      <c r="B41" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="C41" s="1" t="s">
+      <c r="C41" s="2" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A42" t="s">
+      <c r="A42" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="C42" s="1" t="s">
+      <c r="B42" s="1"/>
+      <c r="C42" s="2" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A43" t="s">
+      <c r="A43" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="C43" s="1" t="s">
+      <c r="B43" s="1"/>
+      <c r="C43" s="2" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A44" t="s">
+      <c r="A44" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="C44" s="1" t="s">
+      <c r="B44" s="1"/>
+      <c r="C44" s="2" t="s">
         <v>48</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A45" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="B45" s="1"/>
+      <c r="C45" s="6" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A46" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="B46" s="1"/>
+      <c r="C46" s="1"/>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A47" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="B47" s="1"/>
+      <c r="C47" s="6" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A48" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="B48" s="1"/>
+      <c r="C48" s="6" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A49" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="B49" s="1"/>
+      <c r="C49" s="6" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A50" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="B50" s="1"/>
+      <c r="C50" s="6" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A51" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="B51" s="1"/>
+      <c r="C51" s="6" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A52" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B52" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="C52" s="6" t="s">
+        <v>57</v>
       </c>
     </row>
   </sheetData>
@@ -1092,6 +1289,13 @@
     <hyperlink ref="C42" r:id="rId37" xr:uid="{6804FC99-F1F9-4159-AF5A-7AC03A34D94E}"/>
     <hyperlink ref="C43" r:id="rId38" xr:uid="{5BDFCC58-F060-4AF7-88E6-BAFAB2C8AA8B}"/>
     <hyperlink ref="C44" r:id="rId39" xr:uid="{928EA489-47A4-4243-9A9C-5ED83140354E}"/>
+    <hyperlink ref="C52" r:id="rId40" xr:uid="{B151FF39-D25B-4A71-8AF2-C19D7DDC8256}"/>
+    <hyperlink ref="C51" r:id="rId41" xr:uid="{26CED0B4-9E0D-49EF-BFF0-3DEC354A92CA}"/>
+    <hyperlink ref="C49" r:id="rId42" xr:uid="{113C7C85-C5E7-4294-A3A8-CBF1F0916097}"/>
+    <hyperlink ref="C50" r:id="rId43" xr:uid="{3921751B-5F73-4204-B8B1-9C434872BCE5}"/>
+    <hyperlink ref="C48" r:id="rId44" xr:uid="{169A0EC1-4238-4DC4-B768-3D46594E510C}"/>
+    <hyperlink ref="C47" r:id="rId45" xr:uid="{11EB1AFD-F3FB-4BDE-A36F-FE3A27E7D979}"/>
+    <hyperlink ref="C45" r:id="rId46" xr:uid="{85DA73FA-4FF9-4D36-B1EA-9DD09DFCFBE2}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
